--- a/Output_files/iLPN_search_results.xlsx
+++ b/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1023QA3490</t>
+          <t>VGASN1113QA3680</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10232025QA5520800</t>
+          <t>00V11132025QA8179602</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IN_VAS</t>
+          <t>STORAGE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>CJ2242-100-L</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,10 +543,310 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO10237578</t>
+          <t>PO11133893</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V11132025QA4986703</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CJ2242-100-M</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PO11138664</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11132025QA9951904</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DC4244-291-MISC</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PO11132929</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11132025QA3861905</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DC4244-328-MISC</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PO11132740</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11132025QA7028900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DD9293-100-10.5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PO11137372</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11132025QA7666001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DD9293-100-8</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PO11139762</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -563,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,17 +966,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1023QA3490</t>
+          <t>VGASN1113QA3680</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V10232025QA5520800</t>
+          <t>00V11132025QA8179602</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900000751</t>
+          <t>900001103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -686,43 +986,374 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>CJ2242-100-L</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>31.563</v>
       </c>
       <c r="M2" t="n">
-        <v>28314</v>
+        <v>85926.16</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO10237578</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1507000000</t>
-        </is>
-      </c>
+          <t>PO11133893</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1506000000</t>
+          <t>2401098113</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V11132025QA4986703</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900001103</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CJ2242-100-M</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="M3" t="n">
+        <v>42395.76</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>PO11138664</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2401098114</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00V11132025QA9951904</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001103</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DC4244-291-MISC</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>205563.15</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PO11132929</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2401098115</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00V11132025QA3861905</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900001103</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DC4244-328-MISC</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.465</v>
+      </c>
+      <c r="M5" t="n">
+        <v>19448.572</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PO11132740</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2401098116</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00V11132025QA7028900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900001103</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DD9293-100-10.5</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18482.4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PO11137372</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2401098111</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGASN1113QA3680</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00V11132025QA7666001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900001103</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DD9293-100-8</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30.372</v>
+      </c>
+      <c r="M7" t="n">
+        <v>190160.46</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PO11139762</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2401098112</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -735,118 +1366,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ENVN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ASN_ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>iLPN_ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ItemID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Source_LPN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Condition_Code_Desc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>UserId</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VGASN1023QA3490</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>00V10232025QA5520800</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ilpn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RL - Receiving Lock</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Not Allocated</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Output_files/iLPN_search_results.xlsx
+++ b/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1203QA1590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11132025QA8179602</t>
+          <t>00V12032025QA1811200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STORAGE</t>
+          <t>IN_VAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CJ2242-100-L</t>
+          <t>927205-043-S</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,310 +543,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO11133893</t>
+          <t>PO12033022</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V11132025QA4986703</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CJ2242-100-M</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PO11138664</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11132025QA9951904</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>DC4244-291-MISC</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PO11132929</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11132025QA3861905</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DC4244-328-MISC</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PO11132740</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11132025QA7028900</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>DD9293-100-10.5</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PO11137372</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>vgana3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11132025QA7666001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DD9293-100-8</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PO11139762</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -863,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,17 +666,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1113QA3680</t>
+          <t>VGASN1203QA1590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V11132025QA8179602</t>
+          <t>00V12032025QA1811200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001103</t>
+          <t>900001272</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -986,374 +686,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CJ2242-100-L</t>
+          <t>927205-043-S</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>31.563</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>85926.16</v>
+        <v>1200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO11133893</t>
+          <t>PO12033022</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2401098113</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00V11132025QA4986703</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CJ2242-100-M</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="M3" t="n">
-        <v>42395.76</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>PO11138664</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2401098114</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00V11132025QA9951904</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>DC4244-291-MISC</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="M4" t="n">
-        <v>205563.15</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>PO11132929</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2401098115</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00V11132025QA3861905</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DC4244-328-MISC</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>25.465</v>
-      </c>
-      <c r="M5" t="n">
-        <v>19448.572</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PO11132740</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2401098116</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00V11132025QA7028900</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>DD9293-100-10.5</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>18482.4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>PO11137372</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2401098111</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VGASN1113QA3680</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00V11132025QA7666001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>900001103</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DD9293-100-8</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>63</v>
-      </c>
-      <c r="L7" t="n">
-        <v>30.372</v>
-      </c>
-      <c r="M7" t="n">
-        <v>190160.46</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PO11139762</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2401098112</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1366,9 +727,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENVN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASN_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iLPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_LPN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Condition_Code_Desc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserId</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGASN1203QA1590</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00V12032025QA1811200</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>927205-043-S</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PW - In-VAS PI work</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00887232066765</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGASN1203QA1590</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00V12032025QA1811200</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>927205-043-S</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Allocated</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00887232066765</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Output_files/iLPN_search_results.xlsx
+++ b/Output_files/iLPN_search_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055219</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251203004902000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -543,10 +543,1150 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PO12033022</t>
+          <t>3503907275</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20251203004902000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20251203004902000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20251203004902000004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20251203004902000005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251203004902000006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20251203004902000007</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251203004902000008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251203004902000009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251203004902000010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IN_VAS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251203004902000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251203004902000012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20251203004902000013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20251203004902000014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20251203004902000015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20251203004902000016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20251203004902000017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20251203004902000018</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20251203004902000019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20251203004902000020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STORAGE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
@@ -563,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,55 +1806,1372 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055219</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251203004902000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>900001272</t>
+          <t>900001284</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>1200</v>
+        <v>64000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PO12033022</t>
+          <t>3503907275</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20251203004902000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20251203004902000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20251203004902000006</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20251203004902000005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251203004902000008</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20251203004902000004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251203004902000007</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251203004902000009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251203004902000010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>40</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1907000000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2401098155</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251203004902000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251203004902000015</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20251203004902000019</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20251203004902000012</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>40</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" t="n">
+        <v>40</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20251203004902000017</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" t="n">
+        <v>40</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20251203004902000014</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>40</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20251203004902000018</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>40</v>
+      </c>
+      <c r="J18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K18" t="n">
+        <v>40</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20251203004902000013</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>40</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20251203004902000016</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" t="n">
+        <v>40</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20251203004902000020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>900001284</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>40</v>
+      </c>
+      <c r="J21" t="n">
+        <v>40</v>
+      </c>
+      <c r="K21" t="n">
+        <v>40</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>64000</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3503907275</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2401098156</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -727,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,22 +3262,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055219</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251203004902000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -829,22 +3286,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PW - In-VAS PI work</t>
+          <t>RL - Receiving lock</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Not Allocated</t>
+          <t>Allocated</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00887232066765</t>
+          <t>00194276397220</t>
         </is>
       </c>
     </row>
@@ -861,22 +3318,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VGASN1203QA1590</t>
+          <t>0215055219</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00V12032025QA1811200</t>
+          <t>20251203004902000002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>927205-043-S</t>
+          <t>432997-128-13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -890,17 +3347,1025 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>nike-nas-user</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Not Allocated</t>
+          <t>Allocated</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00887232066765</t>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20251203004902000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20251203004902000004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20251203004902000005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251203004902000006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20251203004902000007</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251203004902000008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251203004902000009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251203004902000010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>432997-128-13</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00194276397220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251203004902000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251203004902000012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20251203004902000013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20251203004902000014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20251203004902000015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20251203004902000016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20251203004902000017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20251203004902000018</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20251203004902000019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0215055219</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20251203004902000020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>432997-128-14</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ilpn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RL - Receiving lock</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Allocated</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>00194276397237</t>
         </is>
       </c>
     </row>
